--- a/static/data/exports/Retro_MN_GE_2024.xlsx
+++ b/static/data/exports/Retro_MN_GE_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>57</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
@@ -638,8 +651,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>59</v>
+      </c>
       <c r="Q3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>53</v>
@@ -700,6 +726,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>32</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -762,6 +801,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>45</v>
+      </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
@@ -824,6 +876,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>52</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -948,6 +1013,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>69</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
@@ -1010,8 +1088,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>59</v>
+      </c>
       <c r="Q9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>53</v>
@@ -1072,6 +1163,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>57</v>
+      </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1238,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>32</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,6 +1313,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>45</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1450,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>52</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1525,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>69</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1600,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>57</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1506,8 +1675,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>59</v>
+      </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>53</v>
@@ -1568,6 +1750,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>32</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1630,6 +1825,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>45</v>
+      </c>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
@@ -1692,6 +1900,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>52</v>
+      </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +2037,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>69</v>
+      </c>
       <c r="Q22" t="b">
         <v>0</v>
       </c>
@@ -1878,6 +2112,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>57</v>
+      </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
@@ -1940,8 +2187,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>59</v>
+      </c>
       <c r="Q24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>53</v>
@@ -2002,6 +2262,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>32</v>
+      </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2064,6 +2337,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>45</v>
+      </c>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
@@ -2126,6 +2412,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>52</v>
+      </c>
       <c r="Q27" t="b">
         <v>0</v>
       </c>
@@ -2250,6 +2549,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>69</v>
+      </c>
       <c r="Q29" t="b">
         <v>0</v>
       </c>
@@ -2312,6 +2624,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>57</v>
+      </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
@@ -2374,8 +2699,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>59</v>
+      </c>
       <c r="Q31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>53</v>
@@ -2436,6 +2774,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>32</v>
+      </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2498,6 +2849,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>45</v>
+      </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
@@ -2560,6 +2924,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>52</v>
+      </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
@@ -2684,6 +3061,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>69</v>
+      </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -2746,8 +3136,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>59</v>
+      </c>
       <c r="Q37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>53</v>
@@ -2808,6 +3211,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>57</v>
+      </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
@@ -2870,6 +3286,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>32</v>
+      </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
@@ -2932,6 +3361,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>45</v>
+      </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
@@ -2994,6 +3436,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>52</v>
+      </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
@@ -3118,6 +3573,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>69</v>
+      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3180,8 +3648,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>59</v>
+      </c>
       <c r="Q44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>53</v>
@@ -3242,6 +3723,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>57</v>
+      </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
@@ -3304,6 +3798,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>32</v>
+      </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
@@ -3366,6 +3873,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>45</v>
+      </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3428,6 +3948,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>52</v>
+      </c>
       <c r="Q48" t="b">
         <v>0</v>
       </c>
@@ -3552,6 +4085,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>69</v>
+      </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
@@ -3614,6 +4160,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>57</v>
+      </c>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
@@ -3676,8 +4235,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>59</v>
+      </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>53</v>
@@ -3738,6 +4310,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>32</v>
+      </c>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
@@ -3800,6 +4385,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>45</v>
+      </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
@@ -3862,6 +4460,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>52</v>
+      </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
@@ -3986,6 +4597,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>69</v>
+      </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
@@ -4048,6 +4672,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>57</v>
+      </c>
       <c r="Q58" t="b">
         <v>0</v>
       </c>
@@ -4110,8 +4747,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>59</v>
+      </c>
       <c r="Q59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>53</v>
@@ -4172,6 +4822,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>32</v>
+      </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
@@ -4234,6 +4897,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>45</v>
+      </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4358,6 +5034,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>52</v>
+      </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
@@ -4420,6 +5109,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>69</v>
+      </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
@@ -4482,6 +5184,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>57</v>
+      </c>
       <c r="Q65" t="b">
         <v>0</v>
       </c>
@@ -4544,6 +5259,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>32</v>
+      </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -4606,8 +5334,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>59</v>
+      </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>53</v>
@@ -4668,6 +5409,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>45</v>
+      </c>
       <c r="Q68" t="b">
         <v>0</v>
       </c>
@@ -4730,6 +5484,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>52</v>
+      </c>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
@@ -4854,6 +5621,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>69</v>
+      </c>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
@@ -4916,6 +5696,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>57</v>
+      </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
@@ -4978,8 +5771,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>59</v>
+      </c>
       <c r="Q73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>53</v>
@@ -5040,6 +5846,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>32</v>
+      </c>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
@@ -5102,6 +5921,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>45</v>
+      </c>
       <c r="Q75" t="b">
         <v>0</v>
       </c>
@@ -5226,6 +6058,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>52</v>
+      </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
@@ -5288,6 +6133,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>69</v>
+      </c>
       <c r="Q78" t="b">
         <v>0</v>
       </c>
@@ -5350,6 +6208,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>57</v>
+      </c>
       <c r="Q79" t="b">
         <v>0</v>
       </c>
@@ -5412,6 +6283,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>32</v>
+      </c>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
@@ -5474,8 +6358,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>59</v>
+      </c>
       <c r="Q81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>53</v>
@@ -5536,6 +6433,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>45</v>
+      </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -5660,6 +6570,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>52</v>
+      </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -5722,6 +6645,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>69</v>
+      </c>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
@@ -5784,6 +6720,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>57</v>
+      </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
@@ -5846,8 +6795,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>59</v>
+      </c>
       <c r="Q87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>53</v>
@@ -5908,6 +6870,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>32</v>
+      </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
@@ -5970,6 +6945,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>45</v>
+      </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
@@ -6032,6 +7020,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>52</v>
+      </c>
       <c r="Q90" t="b">
         <v>0</v>
       </c>
@@ -6156,6 +7157,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>69</v>
+      </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
@@ -6218,6 +7232,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>57</v>
+      </c>
       <c r="Q93" t="b">
         <v>0</v>
       </c>
@@ -6280,8 +7307,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>59</v>
+      </c>
       <c r="Q94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>53</v>
@@ -6342,6 +7382,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>32</v>
+      </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
@@ -6404,6 +7457,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>45</v>
+      </c>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
@@ -6528,6 +7594,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>52</v>
+      </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
@@ -6590,6 +7669,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>69</v>
+      </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
@@ -6652,6 +7744,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>57</v>
+      </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
@@ -6714,8 +7819,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>59</v>
+      </c>
       <c r="Q101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>53</v>
@@ -6776,6 +7894,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>32</v>
+      </c>
       <c r="Q102" t="b">
         <v>0</v>
       </c>
@@ -6838,6 +7969,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>45</v>
+      </c>
       <c r="Q103" t="b">
         <v>0</v>
       </c>
@@ -6962,6 +8106,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>52</v>
+      </c>
       <c r="Q105" t="b">
         <v>0</v>
       </c>
@@ -7024,6 +8181,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>69</v>
+      </c>
       <c r="Q106" t="b">
         <v>0</v>
       </c>
@@ -7086,8 +8256,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>59</v>
+      </c>
       <c r="Q107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
         <v>53</v>
@@ -7148,6 +8331,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>57</v>
+      </c>
       <c r="Q108" t="b">
         <v>0</v>
       </c>
@@ -7210,6 +8406,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>32</v>
+      </c>
       <c r="Q109" t="b">
         <v>0</v>
       </c>
@@ -7272,6 +8481,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>45</v>
+      </c>
       <c r="Q110" t="b">
         <v>0</v>
       </c>
@@ -7334,6 +8556,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>52</v>
+      </c>
       <c r="Q111" t="b">
         <v>0</v>
       </c>
@@ -7458,6 +8693,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>69</v>
+      </c>
       <c r="Q113" t="b">
         <v>0</v>
       </c>
@@ -7520,6 +8768,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P114" t="n">
+        <v>57</v>
+      </c>
       <c r="Q114" t="b">
         <v>0</v>
       </c>
@@ -7582,6 +8843,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>32</v>
+      </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
@@ -7644,8 +8918,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>59</v>
+      </c>
       <c r="Q116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
         <v>53</v>
@@ -7706,6 +8993,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>45</v>
+      </c>
       <c r="Q117" t="b">
         <v>0</v>
       </c>
@@ -7768,6 +9068,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>52</v>
+      </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
@@ -7892,6 +9205,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>69</v>
+      </c>
       <c r="Q120" t="b">
         <v>0</v>
       </c>
@@ -7954,8 +9280,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>59</v>
+      </c>
       <c r="Q121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>53</v>
@@ -8016,6 +9355,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>57</v>
+      </c>
       <c r="Q122" t="b">
         <v>0</v>
       </c>
@@ -8078,6 +9430,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>32</v>
+      </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
@@ -8140,6 +9505,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>45</v>
+      </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
@@ -8202,6 +9580,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>52</v>
+      </c>
       <c r="Q125" t="b">
         <v>0</v>
       </c>
@@ -8326,6 +9717,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>69</v>
+      </c>
       <c r="Q127" t="b">
         <v>0</v>
       </c>
@@ -8388,6 +9792,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>57</v>
+      </c>
       <c r="Q128" t="b">
         <v>0</v>
       </c>
@@ -8450,8 +9867,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>59</v>
+      </c>
       <c r="Q129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>53</v>
@@ -8512,6 +9942,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>32</v>
+      </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
@@ -8574,6 +10017,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>45</v>
+      </c>
       <c r="Q131" t="b">
         <v>0</v>
       </c>
@@ -8636,6 +10092,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>52</v>
+      </c>
       <c r="Q132" t="b">
         <v>0</v>
       </c>
@@ -8760,6 +10229,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>69</v>
+      </c>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
@@ -8822,6 +10304,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>57</v>
+      </c>
       <c r="Q135" t="b">
         <v>0</v>
       </c>
@@ -8884,8 +10379,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>59</v>
+      </c>
       <c r="Q136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>53</v>
@@ -8946,6 +10454,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>32</v>
+      </c>
       <c r="Q137" t="b">
         <v>0</v>
       </c>
@@ -9008,6 +10529,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>45</v>
+      </c>
       <c r="Q138" t="b">
         <v>0</v>
       </c>
@@ -9070,6 +10604,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>52</v>
+      </c>
       <c r="Q139" t="b">
         <v>0</v>
       </c>
@@ -9194,6 +10741,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>69</v>
+      </c>
       <c r="Q141" t="b">
         <v>0</v>
       </c>
@@ -9256,6 +10816,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>57</v>
+      </c>
       <c r="Q142" t="b">
         <v>0</v>
       </c>
@@ -9318,8 +10891,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>59</v>
+      </c>
       <c r="Q143" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>53</v>
@@ -9380,6 +10966,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>32</v>
+      </c>
       <c r="Q144" t="b">
         <v>0</v>
       </c>
@@ -9442,6 +11041,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>45</v>
+      </c>
       <c r="Q145" t="b">
         <v>0</v>
       </c>
@@ -9504,6 +11116,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>52</v>
+      </c>
       <c r="Q146" t="b">
         <v>0</v>
       </c>
@@ -9628,6 +11253,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>69</v>
+      </c>
       <c r="Q148" t="b">
         <v>0</v>
       </c>
@@ -9690,6 +11328,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>57</v>
+      </c>
       <c r="Q149" t="b">
         <v>0</v>
       </c>
@@ -9752,8 +11403,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>59</v>
+      </c>
       <c r="Q150" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
         <v>53</v>
@@ -9814,6 +11478,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>32</v>
+      </c>
       <c r="Q151" t="b">
         <v>0</v>
       </c>
@@ -9876,6 +11553,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>45</v>
+      </c>
       <c r="Q152" t="b">
         <v>0</v>
       </c>
@@ -9938,6 +11628,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>52</v>
+      </c>
       <c r="Q153" t="b">
         <v>0</v>
       </c>
@@ -10062,6 +11765,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>69</v>
+      </c>
       <c r="Q155" t="b">
         <v>0</v>
       </c>
@@ -10124,6 +11840,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>57</v>
+      </c>
       <c r="Q156" t="b">
         <v>0</v>
       </c>
@@ -10186,8 +11915,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>59</v>
+      </c>
       <c r="Q157" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>53</v>
@@ -10248,6 +11990,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P158" t="n">
+        <v>32</v>
+      </c>
       <c r="Q158" t="b">
         <v>0</v>
       </c>
@@ -10310,6 +12065,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>45</v>
+      </c>
       <c r="Q159" t="b">
         <v>0</v>
       </c>
@@ -10372,6 +12140,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>52</v>
+      </c>
       <c r="Q160" t="b">
         <v>0</v>
       </c>
@@ -10496,6 +12277,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>69</v>
+      </c>
       <c r="Q162" t="b">
         <v>0</v>
       </c>
@@ -10558,8 +12352,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>59</v>
+      </c>
       <c r="Q163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>53</v>
@@ -10620,6 +12427,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>57</v>
+      </c>
       <c r="Q164" t="b">
         <v>0</v>
       </c>
@@ -10682,6 +12502,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>32</v>
+      </c>
       <c r="Q165" t="b">
         <v>0</v>
       </c>
@@ -10744,6 +12577,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>45</v>
+      </c>
       <c r="Q166" t="b">
         <v>0</v>
       </c>
@@ -10806,6 +12652,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>52</v>
+      </c>
       <c r="Q167" t="b">
         <v>0</v>
       </c>
@@ -10930,6 +12789,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>69</v>
+      </c>
       <c r="Q169" t="b">
         <v>0</v>
       </c>
@@ -10992,8 +12864,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>59</v>
+      </c>
       <c r="Q170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>53</v>
@@ -11054,6 +12939,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>57</v>
+      </c>
       <c r="Q171" t="b">
         <v>0</v>
       </c>
@@ -11116,6 +13014,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>32</v>
+      </c>
       <c r="Q172" t="b">
         <v>0</v>
       </c>
@@ -11178,6 +13089,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P173" t="n">
+        <v>45</v>
+      </c>
       <c r="Q173" t="b">
         <v>0</v>
       </c>
@@ -11240,6 +13164,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>52</v>
+      </c>
       <c r="Q174" t="b">
         <v>0</v>
       </c>
@@ -11364,6 +13301,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>69</v>
+      </c>
       <c r="Q176" t="b">
         <v>0</v>
       </c>
@@ -11426,8 +13376,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>59</v>
+      </c>
       <c r="Q177" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R177" t="n">
         <v>53</v>
@@ -11488,6 +13451,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>57</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
@@ -11550,6 +13526,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>32</v>
+      </c>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
@@ -11612,6 +13601,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P180" t="n">
+        <v>45</v>
+      </c>
       <c r="Q180" t="b">
         <v>0</v>
       </c>
@@ -11674,6 +13676,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>52</v>
+      </c>
       <c r="Q181" t="b">
         <v>0</v>
       </c>
@@ -11798,6 +13813,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>69</v>
+      </c>
       <c r="Q183" t="b">
         <v>0</v>
       </c>
@@ -11860,6 +13888,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>57</v>
+      </c>
       <c r="Q184" t="b">
         <v>0</v>
       </c>
@@ -11922,8 +13963,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>59</v>
+      </c>
       <c r="Q185" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
         <v>53</v>
@@ -11984,6 +14038,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>32</v>
+      </c>
       <c r="Q186" t="b">
         <v>0</v>
       </c>
@@ -12046,6 +14113,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>45</v>
+      </c>
       <c r="Q187" t="b">
         <v>0</v>
       </c>
@@ -12108,6 +14188,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>52</v>
+      </c>
       <c r="Q188" t="b">
         <v>0</v>
       </c>
@@ -12232,6 +14325,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P190" t="n">
+        <v>69</v>
+      </c>
       <c r="Q190" t="b">
         <v>0</v>
       </c>
@@ -12294,8 +14400,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>59</v>
+      </c>
       <c r="Q191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R191" t="n">
         <v>53</v>
@@ -12356,6 +14475,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>57</v>
+      </c>
       <c r="Q192" t="b">
         <v>0</v>
       </c>
@@ -12418,6 +14550,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>32</v>
+      </c>
       <c r="Q193" t="b">
         <v>0</v>
       </c>
@@ -12480,6 +14625,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>45</v>
+      </c>
       <c r="Q194" t="b">
         <v>0</v>
       </c>
@@ -12542,6 +14700,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>52</v>
+      </c>
       <c r="Q195" t="b">
         <v>0</v>
       </c>
@@ -12666,6 +14837,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>69</v>
+      </c>
       <c r="Q197" t="b">
         <v>0</v>
       </c>
@@ -12728,6 +14912,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P198" t="n">
+        <v>57</v>
+      </c>
       <c r="Q198" t="b">
         <v>0</v>
       </c>
@@ -12790,8 +14987,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>59</v>
+      </c>
       <c r="Q199" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R199" t="n">
         <v>53</v>
@@ -12852,6 +15062,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>32</v>
+      </c>
       <c r="Q200" t="b">
         <v>0</v>
       </c>
@@ -12914,6 +15137,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>45</v>
+      </c>
       <c r="Q201" t="b">
         <v>0</v>
       </c>
@@ -12976,6 +15212,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>52</v>
+      </c>
       <c r="Q202" t="b">
         <v>0</v>
       </c>
@@ -13100,6 +15349,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>69</v>
+      </c>
       <c r="Q204" t="b">
         <v>0</v>
       </c>
@@ -13162,6 +15424,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>57</v>
+      </c>
       <c r="Q205" t="b">
         <v>0</v>
       </c>
@@ -13224,8 +15499,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>59</v>
+      </c>
       <c r="Q206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
         <v>53</v>
@@ -13286,6 +15574,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>32</v>
+      </c>
       <c r="Q207" t="b">
         <v>0</v>
       </c>
@@ -13348,6 +15649,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>45</v>
+      </c>
       <c r="Q208" t="b">
         <v>0</v>
       </c>
@@ -13410,6 +15724,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>52</v>
+      </c>
       <c r="Q209" t="b">
         <v>0</v>
       </c>
@@ -13534,6 +15861,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>69</v>
+      </c>
       <c r="Q211" t="b">
         <v>0</v>
       </c>
@@ -13596,6 +15936,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>57</v>
+      </c>
       <c r="Q212" t="b">
         <v>0</v>
       </c>
@@ -13658,8 +16011,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>59</v>
+      </c>
       <c r="Q213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
         <v>53</v>
@@ -13720,6 +16086,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>32</v>
+      </c>
       <c r="Q214" t="b">
         <v>0</v>
       </c>
@@ -13782,6 +16161,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>45</v>
+      </c>
       <c r="Q215" t="b">
         <v>0</v>
       </c>
@@ -13844,6 +16236,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>52</v>
+      </c>
       <c r="Q216" t="b">
         <v>0</v>
       </c>
@@ -13968,6 +16373,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>69</v>
+      </c>
       <c r="Q218" t="b">
         <v>0</v>
       </c>
@@ -14030,6 +16448,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>57</v>
+      </c>
       <c r="Q219" t="b">
         <v>0</v>
       </c>
@@ -14092,8 +16523,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P220" t="n">
+        <v>59</v>
+      </c>
       <c r="Q220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
         <v>53</v>
@@ -14154,6 +16598,19 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>32</v>
+      </c>
       <c r="Q221" t="b">
         <v>0</v>
       </c>
@@ -14216,6 +16673,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>45</v>
+      </c>
       <c r="Q222" t="b">
         <v>0</v>
       </c>
@@ -14278,6 +16748,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>52</v>
+      </c>
       <c r="Q223" t="b">
         <v>0</v>
       </c>
@@ -14402,6 +16885,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>69</v>
+      </c>
       <c r="Q225" t="b">
         <v>0</v>
       </c>
@@ -14464,6 +16960,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>50</v>
+      </c>
       <c r="Q226" t="b">
         <v>0</v>
       </c>
@@ -14526,8 +17035,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P227" t="n">
+        <v>62</v>
+      </c>
       <c r="Q227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R227" t="n">
         <v>53</v>
@@ -14650,6 +17172,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>60</v>
+      </c>
       <c r="Q229" t="b">
         <v>0</v>
       </c>
@@ -14712,6 +17247,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>38</v>
+      </c>
       <c r="Q230" t="b">
         <v>0</v>
       </c>
@@ -14774,6 +17322,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>50</v>
+      </c>
       <c r="Q231" t="b">
         <v>0</v>
       </c>
@@ -14836,8 +17397,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>62</v>
+      </c>
       <c r="Q232" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R232" t="n">
         <v>53</v>
@@ -14960,6 +17534,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>60</v>
+      </c>
       <c r="Q234" t="b">
         <v>0</v>
       </c>
@@ -15022,6 +17609,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>38</v>
+      </c>
       <c r="Q235" t="b">
         <v>0</v>
       </c>
@@ -15084,6 +17684,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P236" t="n">
+        <v>50</v>
+      </c>
       <c r="Q236" t="b">
         <v>0</v>
       </c>
@@ -15146,8 +17759,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>62</v>
+      </c>
       <c r="Q237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R237" t="n">
         <v>53</v>
@@ -15270,6 +17896,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>60</v>
+      </c>
       <c r="Q239" t="b">
         <v>0</v>
       </c>
@@ -15332,6 +17971,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>38</v>
+      </c>
       <c r="Q240" t="b">
         <v>0</v>
       </c>
@@ -15394,6 +18046,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>50</v>
+      </c>
       <c r="Q241" t="b">
         <v>0</v>
       </c>
@@ -15456,8 +18121,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P242" t="n">
+        <v>62</v>
+      </c>
       <c r="Q242" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
         <v>53</v>
@@ -15580,6 +18258,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>60</v>
+      </c>
       <c r="Q244" t="b">
         <v>0</v>
       </c>
@@ -15642,6 +18333,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>38</v>
+      </c>
       <c r="Q245" t="b">
         <v>0</v>
       </c>
@@ -15704,6 +18408,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>50</v>
+      </c>
       <c r="Q246" t="b">
         <v>0</v>
       </c>
@@ -15766,8 +18483,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>62</v>
+      </c>
       <c r="Q247" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
         <v>53</v>
@@ -15890,6 +18620,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>60</v>
+      </c>
       <c r="Q249" t="b">
         <v>0</v>
       </c>
@@ -15952,6 +18695,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>38</v>
+      </c>
       <c r="Q250" t="b">
         <v>0</v>
       </c>
@@ -16014,8 +18770,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P251" t="n">
+        <v>62</v>
+      </c>
       <c r="Q251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
         <v>53</v>
@@ -16076,6 +18845,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>50</v>
+      </c>
       <c r="Q252" t="b">
         <v>0</v>
       </c>
@@ -16200,6 +18982,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P254" t="n">
+        <v>60</v>
+      </c>
       <c r="Q254" t="b">
         <v>0</v>
       </c>
@@ -16262,6 +19057,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>38</v>
+      </c>
       <c r="Q255" t="b">
         <v>0</v>
       </c>
@@ -16324,8 +19132,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>62</v>
+      </c>
       <c r="Q256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
         <v>53</v>
@@ -16386,6 +19207,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>50</v>
+      </c>
       <c r="Q257" t="b">
         <v>0</v>
       </c>
@@ -16510,6 +19344,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>38</v>
+      </c>
       <c r="Q259" t="b">
         <v>0</v>
       </c>
@@ -16572,6 +19419,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>60</v>
+      </c>
       <c r="Q260" t="b">
         <v>0</v>
       </c>
@@ -16634,6 +19494,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>50</v>
+      </c>
       <c r="Q261" t="b">
         <v>0</v>
       </c>
@@ -16696,8 +19569,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>62</v>
+      </c>
       <c r="Q262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R262" t="n">
         <v>53</v>
@@ -16820,6 +19706,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>60</v>
+      </c>
       <c r="Q264" t="b">
         <v>0</v>
       </c>
@@ -16882,6 +19781,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>38</v>
+      </c>
       <c r="Q265" t="b">
         <v>0</v>
       </c>
@@ -16944,8 +19856,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>62</v>
+      </c>
       <c r="Q266" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
         <v>53</v>
@@ -17006,6 +19931,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>50</v>
+      </c>
       <c r="Q267" t="b">
         <v>0</v>
       </c>
@@ -17068,6 +20006,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>60</v>
+      </c>
       <c r="Q268" t="b">
         <v>0</v>
       </c>
@@ -17130,6 +20081,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>38</v>
+      </c>
       <c r="Q269" t="b">
         <v>0</v>
       </c>
@@ -17254,8 +20218,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>62</v>
+      </c>
       <c r="Q271" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R271" t="n">
         <v>53</v>
@@ -17316,6 +20293,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>50</v>
+      </c>
       <c r="Q272" t="b">
         <v>0</v>
       </c>
@@ -17378,6 +20368,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>60</v>
+      </c>
       <c r="Q273" t="b">
         <v>0</v>
       </c>
@@ -17440,6 +20443,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>38</v>
+      </c>
       <c r="Q274" t="b">
         <v>0</v>
       </c>
@@ -17564,8 +20580,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>62</v>
+      </c>
       <c r="Q276" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R276" t="n">
         <v>53</v>
@@ -17626,6 +20655,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>50</v>
+      </c>
       <c r="Q277" t="b">
         <v>0</v>
       </c>
@@ -17688,6 +20730,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>60</v>
+      </c>
       <c r="Q278" t="b">
         <v>0</v>
       </c>
@@ -17750,6 +20805,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>38</v>
+      </c>
       <c r="Q279" t="b">
         <v>0</v>
       </c>
@@ -17874,8 +20942,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>62</v>
+      </c>
       <c r="Q281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R281" t="n">
         <v>53</v>
@@ -17936,6 +21017,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>50</v>
+      </c>
       <c r="Q282" t="b">
         <v>0</v>
       </c>
@@ -17998,6 +21092,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>60</v>
+      </c>
       <c r="Q283" t="b">
         <v>0</v>
       </c>
@@ -18060,6 +21167,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>38</v>
+      </c>
       <c r="Q284" t="b">
         <v>0</v>
       </c>
@@ -18184,8 +21304,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>62</v>
+      </c>
       <c r="Q286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R286" t="n">
         <v>53</v>
@@ -18246,6 +21379,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>50</v>
+      </c>
       <c r="Q287" t="b">
         <v>0</v>
       </c>
@@ -18308,6 +21454,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>38</v>
+      </c>
       <c r="Q288" t="b">
         <v>0</v>
       </c>
@@ -18370,6 +21529,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>60</v>
+      </c>
       <c r="Q289" t="b">
         <v>0</v>
       </c>
@@ -18494,6 +21666,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>50</v>
+      </c>
       <c r="Q291" t="b">
         <v>0</v>
       </c>
@@ -18556,8 +21741,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>62</v>
+      </c>
       <c r="Q292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R292" t="n">
         <v>53</v>
@@ -18618,6 +21816,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>60</v>
+      </c>
       <c r="Q293" t="b">
         <v>0</v>
       </c>
@@ -18680,6 +21891,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>38</v>
+      </c>
       <c r="Q294" t="b">
         <v>0</v>
       </c>
@@ -18804,6 +22028,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>60</v>
+      </c>
       <c r="Q296" t="b">
         <v>0</v>
       </c>
@@ -18866,8 +22103,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>62</v>
+      </c>
       <c r="Q297" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R297" t="n">
         <v>53</v>
@@ -18928,6 +22178,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>50</v>
+      </c>
       <c r="Q298" t="b">
         <v>0</v>
       </c>
@@ -18990,6 +22253,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>38</v>
+      </c>
       <c r="Q299" t="b">
         <v>0</v>
       </c>
@@ -19114,6 +22390,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>60</v>
+      </c>
       <c r="Q301" t="b">
         <v>0</v>
       </c>
@@ -19176,8 +22465,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>62</v>
+      </c>
       <c r="Q302" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R302" t="n">
         <v>53</v>
@@ -19238,6 +22540,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>50</v>
+      </c>
       <c r="Q303" t="b">
         <v>0</v>
       </c>
@@ -19300,6 +22615,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P304" t="n">
+        <v>38</v>
+      </c>
       <c r="Q304" t="b">
         <v>0</v>
       </c>
@@ -19424,8 +22752,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>62</v>
+      </c>
       <c r="Q306" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R306" t="n">
         <v>53</v>
@@ -19486,6 +22827,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>60</v>
+      </c>
       <c r="Q307" t="b">
         <v>0</v>
       </c>
@@ -19548,6 +22902,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>50</v>
+      </c>
       <c r="Q308" t="b">
         <v>0</v>
       </c>
@@ -19610,6 +22977,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>38</v>
+      </c>
       <c r="Q309" t="b">
         <v>0</v>
       </c>
@@ -19734,8 +23114,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>62</v>
+      </c>
       <c r="Q311" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R311" t="n">
         <v>53</v>
@@ -19796,6 +23189,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>60</v>
+      </c>
       <c r="Q312" t="b">
         <v>0</v>
       </c>
@@ -19858,6 +23264,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>50</v>
+      </c>
       <c r="Q313" t="b">
         <v>0</v>
       </c>
@@ -19920,6 +23339,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>38</v>
+      </c>
       <c r="Q314" t="b">
         <v>0</v>
       </c>
@@ -20044,8 +23476,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>62</v>
+      </c>
       <c r="Q316" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R316" t="n">
         <v>53</v>
@@ -20106,6 +23551,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>50</v>
+      </c>
       <c r="Q317" t="b">
         <v>0</v>
       </c>
@@ -20168,6 +23626,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>60</v>
+      </c>
       <c r="Q318" t="b">
         <v>0</v>
       </c>
@@ -20230,6 +23701,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>38</v>
+      </c>
       <c r="Q319" t="b">
         <v>0</v>
       </c>
@@ -20354,8 +23838,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>62</v>
+      </c>
       <c r="Q321" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R321" t="n">
         <v>53</v>
@@ -20416,6 +23913,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>50</v>
+      </c>
       <c r="Q322" t="b">
         <v>0</v>
       </c>
@@ -20478,6 +23988,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>38</v>
+      </c>
       <c r="Q323" t="b">
         <v>0</v>
       </c>
@@ -20540,6 +24063,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>60</v>
+      </c>
       <c r="Q324" t="b">
         <v>0</v>
       </c>
@@ -20664,8 +24200,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>62</v>
+      </c>
       <c r="Q326" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R326" t="n">
         <v>53</v>
@@ -20726,6 +24275,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P327" t="n">
+        <v>50</v>
+      </c>
       <c r="Q327" t="b">
         <v>0</v>
       </c>
@@ -20788,6 +24350,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>38</v>
+      </c>
       <c r="Q328" t="b">
         <v>0</v>
       </c>
@@ -20850,6 +24425,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>60</v>
+      </c>
       <c r="Q329" t="b">
         <v>0</v>
       </c>
@@ -20974,8 +24562,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>62</v>
+      </c>
       <c r="Q331" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R331" t="n">
         <v>53</v>
@@ -21036,6 +24637,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>50</v>
+      </c>
       <c r="Q332" t="b">
         <v>0</v>
       </c>
@@ -21098,6 +24712,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>38</v>
+      </c>
       <c r="Q333" t="b">
         <v>0</v>
       </c>
@@ -21160,6 +24787,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>60</v>
+      </c>
       <c r="Q334" t="b">
         <v>0</v>
       </c>
@@ -21284,6 +24924,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>50</v>
+      </c>
       <c r="Q336" t="b">
         <v>0</v>
       </c>
@@ -21346,8 +24999,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P337" t="n">
+        <v>62</v>
+      </c>
       <c r="Q337" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R337" t="n">
         <v>53</v>
@@ -21408,6 +25074,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>60</v>
+      </c>
       <c r="Q338" t="b">
         <v>0</v>
       </c>
@@ -21470,6 +25149,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>38</v>
+      </c>
       <c r="Q339" t="b">
         <v>0</v>
       </c>
@@ -21594,6 +25286,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>50</v>
+      </c>
       <c r="Q341" t="b">
         <v>0</v>
       </c>
@@ -21656,6 +25361,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>60</v>
+      </c>
       <c r="Q342" t="b">
         <v>0</v>
       </c>
@@ -21718,6 +25436,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>38</v>
+      </c>
       <c r="Q343" t="b">
         <v>0</v>
       </c>
@@ -21780,8 +25511,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>62</v>
+      </c>
       <c r="Q344" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R344" t="n">
         <v>53</v>
@@ -21904,6 +25648,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>50</v>
+      </c>
       <c r="Q346" t="b">
         <v>0</v>
       </c>
@@ -21966,8 +25723,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>62</v>
+      </c>
       <c r="Q347" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R347" t="n">
         <v>53</v>
@@ -22028,6 +25798,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>60</v>
+      </c>
       <c r="Q348" t="b">
         <v>0</v>
       </c>
@@ -22090,6 +25873,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>38</v>
+      </c>
       <c r="Q349" t="b">
         <v>0</v>
       </c>
@@ -22214,6 +26010,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>50</v>
+      </c>
       <c r="Q351" t="b">
         <v>0</v>
       </c>
@@ -22276,6 +26085,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>60</v>
+      </c>
       <c r="Q352" t="b">
         <v>0</v>
       </c>
@@ -22338,6 +26160,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>38</v>
+      </c>
       <c r="Q353" t="b">
         <v>0</v>
       </c>
@@ -22400,8 +26235,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>62</v>
+      </c>
       <c r="Q354" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R354" t="n">
         <v>53</v>
@@ -22524,6 +26372,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P356" t="n">
+        <v>50</v>
+      </c>
       <c r="Q356" t="b">
         <v>0</v>
       </c>
@@ -22586,6 +26447,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>60</v>
+      </c>
       <c r="Q357" t="b">
         <v>0</v>
       </c>
@@ -22648,8 +26522,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P358" t="n">
+        <v>62</v>
+      </c>
       <c r="Q358" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R358" t="n">
         <v>53</v>
@@ -22710,6 +26597,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P359" t="n">
+        <v>38</v>
+      </c>
       <c r="Q359" t="b">
         <v>0</v>
       </c>
@@ -22834,6 +26734,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P361" t="n">
+        <v>50</v>
+      </c>
       <c r="Q361" t="b">
         <v>0</v>
       </c>
@@ -22896,6 +26809,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P362" t="n">
+        <v>60</v>
+      </c>
       <c r="Q362" t="b">
         <v>0</v>
       </c>
@@ -22958,8 +26884,21 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P363" t="n">
+        <v>62</v>
+      </c>
       <c r="Q363" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R363" t="n">
         <v>53</v>
@@ -23020,6 +26959,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P364" t="n">
+        <v>38</v>
+      </c>
       <c r="Q364" t="b">
         <v>0</v>
       </c>
@@ -23144,6 +27096,22 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q366" t="b">
+        <v>0</v>
+      </c>
       <c r="R366" t="n">
         <v>53</v>
       </c>
@@ -23203,6 +27171,22 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P367" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q367" t="b">
+        <v>0</v>
+      </c>
       <c r="R367" t="n">
         <v>53</v>
       </c>
@@ -23262,6 +27246,22 @@
           <t>RPPRINAT</t>
         </is>
       </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P368" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q368" t="b">
+        <v>0</v>
+      </c>
       <c r="R368" t="n">
         <v>53</v>
       </c>
@@ -23321,6 +27321,22 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P369" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q369" t="b">
+        <v>0</v>
+      </c>
       <c r="R369" t="n">
         <v>53</v>
       </c>
@@ -23380,6 +27396,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q370" t="b">
+        <v>0</v>
+      </c>
       <c r="R370" t="n">
         <v>53</v>
       </c>
@@ -23439,6 +27458,22 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q371" t="b">
+        <v>0</v>
+      </c>
       <c r="R371" t="n">
         <v>53</v>
       </c>
@@ -23498,6 +27533,22 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P372" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q372" t="b">
+        <v>0</v>
+      </c>
       <c r="R372" t="n">
         <v>53</v>
       </c>
@@ -23557,6 +27608,22 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q373" t="b">
+        <v>0</v>
+      </c>
       <c r="R373" t="n">
         <v>53</v>
       </c>
@@ -23616,6 +27683,22 @@
           <t>NPF</t>
         </is>
       </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q374" t="b">
+        <v>0</v>
+      </c>
       <c r="R374" t="n">
         <v>53</v>
       </c>
@@ -23675,6 +27758,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q375" t="b">
+        <v>0</v>
+      </c>
       <c r="R375" t="n">
         <v>53</v>
       </c>
@@ -23734,6 +27820,22 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q376" t="b">
+        <v>0</v>
+      </c>
       <c r="R376" t="n">
         <v>53</v>
       </c>
@@ -23792,6 +27894,22 @@
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q377" t="b">
+        <v>0</v>
       </c>
       <c r="R377" t="n">
         <v>53</v>

--- a/static/data/exports/Retro_MN_GE_2024.xlsx
+++ b/static/data/exports/Retro_MN_GE_2024.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -883,7 +883,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P82" t="n">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -6877,7 +6877,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8563,7 +8563,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11260,7 +11260,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11635,7 +11635,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -12796,7 +12796,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P177" t="n">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -13820,7 +13820,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -13895,7 +13895,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P188" t="n">
@@ -14332,7 +14332,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14632,7 +14632,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -15356,7 +15356,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15431,7 +15431,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P205" t="n">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -15943,7 +15943,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P215" t="n">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -16755,7 +16755,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -16967,7 +16967,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17042,7 +17042,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17179,7 +17179,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17254,7 +17254,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P234" t="n">
@@ -17616,7 +17616,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -17903,7 +17903,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -17978,7 +17978,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18053,7 +18053,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18128,7 +18128,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18340,7 +18340,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18415,7 +18415,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -18627,7 +18627,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -18702,7 +18702,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -18777,7 +18777,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -18989,7 +18989,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19064,7 +19064,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19351,7 +19351,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19576,7 +19576,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -19863,7 +19863,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20013,7 +20013,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -20088,7 +20088,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P272" t="n">
@@ -20375,7 +20375,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20450,7 +20450,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -20587,7 +20587,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P276" t="n">
@@ -20662,7 +20662,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -20737,7 +20737,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -20812,7 +20812,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -20949,7 +20949,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P283" t="n">
@@ -21174,7 +21174,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21311,7 +21311,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21386,7 +21386,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P287" t="n">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21536,7 +21536,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -21673,7 +21673,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P291" t="n">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -21823,7 +21823,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22110,7 +22110,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P297" t="n">
@@ -22185,7 +22185,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -22260,7 +22260,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22472,7 +22472,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P304" t="n">
@@ -22759,7 +22759,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23121,7 +23121,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P311" t="n">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23346,7 +23346,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -23483,7 +23483,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -23558,7 +23558,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -23633,7 +23633,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -23708,7 +23708,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -23920,7 +23920,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
@@ -24207,7 +24207,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P327" t="n">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P329" t="n">
@@ -24569,7 +24569,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P332" t="n">
@@ -24719,7 +24719,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -24931,7 +24931,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P337" t="n">
@@ -25081,7 +25081,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P338" t="n">
@@ -25156,7 +25156,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -25293,7 +25293,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P341" t="n">
@@ -25368,7 +25368,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P342" t="n">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P343" t="n">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P344" t="n">
@@ -25655,7 +25655,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P346" t="n">
@@ -25730,7 +25730,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P347" t="n">
@@ -25805,7 +25805,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P348" t="n">
@@ -25880,7 +25880,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -26017,7 +26017,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P351" t="n">
@@ -26092,7 +26092,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P352" t="n">
@@ -26167,7 +26167,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P353" t="n">
@@ -26242,7 +26242,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P354" t="n">
@@ -26379,7 +26379,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P356" t="n">
@@ -26454,7 +26454,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P357" t="n">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P359" t="n">
@@ -26741,7 +26741,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -26816,7 +26816,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P362" t="n">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -27103,7 +27103,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P366" t="n">
@@ -27178,7 +27178,7 @@
       </c>
       <c r="O367" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P367" t="n">
@@ -27253,7 +27253,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P368" t="n">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P369" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P371" t="n">
@@ -27540,7 +27540,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P372" t="n">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -27690,7 +27690,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P374" t="n">
@@ -27827,7 +27827,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P376" t="n">
@@ -27902,7 +27902,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P377" t="n">
